--- a/livrables/Backlog_Fashion_Insta.xlsx
+++ b/livrables/Backlog_Fashion_Insta.xlsx
@@ -145,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -182,6 +182,10 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3247,14 +3251,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="6" min="1" max="1"/>
     <col width="42" customWidth="1" style="6" min="2" max="2"/>
     <col width="28" customWidth="1" style="6" min="3" max="3"/>
     <col width="16" customWidth="1" style="6" min="4" max="4"/>
-    <col width="50" customWidth="1" style="6" min="5" max="5"/>
+    <col width="14" customWidth="1" style="6" min="5" max="5"/>
+    <col width="16" customWidth="1" style="6" min="6" max="6"/>
+    <col width="50" customWidth="1" style="6" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3280,6 +3286,16 @@
       </c>
       <c r="E1" s="7" t="inlineStr">
         <is>
+          <t>Durée (semaines)</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Jours ouvrés dispo</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
           <t>Livrable / Objectif</t>
         </is>
       </c>
@@ -3303,7 +3319,13 @@
       <c r="D2" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>Compte utilisateur opérationnel + pipeline d'ingestion des photos</t>
         </is>
@@ -3328,7 +3350,13 @@
       <c r="D3" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>Garde-robe gérable + détection vêtements (PoC vision)</t>
         </is>
@@ -3353,7 +3381,13 @@
       <c r="D4" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>MVP des deux moteurs IA (garde-robe et préférences/tendances) + panier/commande/paiement : la boucle recommandation → achat est mesurable dès ce sprint</t>
         </is>
@@ -3378,7 +3412,13 @@
       <c r="D5" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>Conformité RGPD validée par le DPO + boucle de feedback</t>
         </is>
@@ -3403,7 +3443,13 @@
       <c r="D6" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>Personnalisation visuelle + purge automatique</t>
         </is>
@@ -3428,9 +3474,27 @@
       <c r="D7" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>Intégration sources externes + recettes finales</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Durée totale du projet</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>13 semaines (5 sprints × 2 sem. + Sprint 3 × 3 sem.)</t>
         </is>
       </c>
     </row>
